--- a/simulations/AON_100/mass_flow_data_AON_100.xlsx
+++ b/simulations/AON_100/mass_flow_data_AON_100.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D628163-54DA-44E1-B306-1C1FF4715B89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A31C84-730F-4DA2-8645-F3738814D651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material streams" sheetId="1" r:id="rId1"/>
@@ -311,7 +311,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,20 +340,6 @@
       <vertAlign val="subscript"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -418,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -452,12 +438,6 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -799,11 +779,11 @@
         <v>23</v>
       </c>
       <c r="D4" s="4">
-        <v>57664.530865398898</v>
+        <v>57664.530874998702</v>
       </c>
       <c r="E4" s="5">
         <f t="shared" ref="E4:E10" si="0">D4/$D$10</f>
-        <v>1.5377177852964765</v>
+        <v>1.5377177852964803</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
@@ -817,11 +797,11 @@
         <v>23</v>
       </c>
       <c r="D5" s="4">
-        <v>30690.502543064998</v>
+        <v>30690.5025481741</v>
       </c>
       <c r="E5" s="5">
         <f t="shared" si="0"/>
-        <v>0.81841178436562534</v>
+        <v>0.81841178436562323</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -853,19 +833,15 @@
         <v>24</v>
       </c>
       <c r="D7" s="4">
-        <v>50854.959326742101</v>
+        <v>50854.959335208201</v>
       </c>
       <c r="E7" s="5">
         <f t="shared" si="0"/>
-        <v>1.3561295696620994</v>
-      </c>
-      <c r="F7" s="18">
-        <f>E7-E6</f>
-        <v>1.3561295696620994</v>
-      </c>
-      <c r="G7" s="1">
-        <f>F7/1000</f>
-        <v>1.3561295696620994E-3</v>
+        <v>1.356129569662101</v>
+      </c>
+      <c r="F7" s="16">
+        <f>E7/1000</f>
+        <v>1.3561295696621009E-3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -896,17 +872,17 @@
       <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="18">
         <v>0</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
@@ -919,562 +895,562 @@
         <v>25</v>
       </c>
       <c r="D10" s="4">
-        <v>37500.074081721701</v>
+        <v>37500.074087964502</v>
       </c>
       <c r="E10" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
     </row>
     <row r="17" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
     </row>
     <row r="18" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
     </row>
     <row r="19" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
     </row>
     <row r="20" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
     </row>
     <row r="22" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
     </row>
     <row r="23" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
     </row>
     <row r="24" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
     </row>
     <row r="25" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
     </row>
     <row r="26" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
     </row>
     <row r="27" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
     </row>
     <row r="28" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
     </row>
     <row r="29" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
     </row>
     <row r="30" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
     </row>
     <row r="31" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
     </row>
     <row r="33" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
     </row>
     <row r="34" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
     </row>
     <row r="35" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
     </row>
     <row r="37" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
     </row>
     <row r="38" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
     </row>
     <row r="39" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
     </row>
     <row r="40" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
     </row>
     <row r="41" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
     </row>
     <row r="42" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
     </row>
     <row r="43" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
     </row>
     <row r="44" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
     </row>
     <row r="45" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
     </row>
     <row r="46" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
     </row>
     <row r="47" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
     </row>
     <row r="48" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
     </row>
     <row r="49" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
     </row>
     <row r="50" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
     </row>
     <row r="51" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
     </row>
     <row r="52" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
     </row>
     <row r="53" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
     </row>
     <row r="54" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
     </row>
     <row r="55" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
     </row>
     <row r="56" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
     </row>
     <row r="57" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
     </row>
     <row r="58" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
     </row>
     <row r="59" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
     </row>
     <row r="60" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
     </row>
     <row r="61" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
     </row>
     <row r="62" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
     </row>
     <row r="63" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
     </row>
     <row r="64" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
     </row>
     <row r="65" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
     </row>
     <row r="66" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
     </row>
     <row r="67" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
     </row>
     <row r="68" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
     </row>
     <row r="69" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
     </row>
     <row r="70" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
     </row>
     <row r="71" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
     </row>
     <row r="72" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
     </row>
     <row r="73" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="17"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
     </row>
     <row r="74" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17"/>
-      <c r="K74" s="17"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
     </row>
     <row r="75" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
     </row>
     <row r="76" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
     </row>
     <row r="77" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
     </row>
     <row r="78" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="K78" s="17"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
     </row>
     <row r="79" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
     </row>
     <row r="80" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15"/>
     </row>
     <row r="81" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
     </row>
     <row r="82" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
-      <c r="J82" s="17"/>
-      <c r="K82" s="17"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
     </row>
     <row r="83" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="17"/>
-      <c r="K83" s="17"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
     </row>
     <row r="84" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
     </row>
     <row r="85" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="17"/>
-      <c r="K85" s="17"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="15"/>
     </row>
     <row r="86" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="15"/>
+      <c r="K86" s="15"/>
     </row>
     <row r="87" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="17"/>
-      <c r="K87" s="17"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
     </row>
     <row r="88" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-      <c r="J88" s="17"/>
-      <c r="K88" s="17"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
     </row>
     <row r="89" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H89" s="17"/>
-      <c r="I89" s="17"/>
-      <c r="J89" s="17"/>
-      <c r="K89" s="17"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15"/>
     </row>
     <row r="90" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H90" s="17"/>
-      <c r="I90" s="17"/>
-      <c r="J90" s="17"/>
-      <c r="K90" s="17"/>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
     </row>
     <row r="91" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
     </row>
     <row r="92" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-      <c r="J92" s="17"/>
-      <c r="K92" s="17"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
     </row>
     <row r="93" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-      <c r="J93" s="17"/>
-      <c r="K93" s="17"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
     </row>
     <row r="94" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H94" s="17"/>
-      <c r="I94" s="17"/>
-      <c r="J94" s="17"/>
-      <c r="K94" s="17"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
     </row>
     <row r="95" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H95" s="17"/>
-      <c r="I95" s="17"/>
-      <c r="J95" s="17"/>
-      <c r="K95" s="17"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
     </row>
     <row r="96" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-      <c r="J96" s="17"/>
-      <c r="K96" s="17"/>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
     </row>
     <row r="97" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-      <c r="J97" s="17"/>
-      <c r="K97" s="17"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
     </row>
     <row r="98" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H98" s="17"/>
-      <c r="I98" s="17"/>
-      <c r="J98" s="17"/>
-      <c r="K98" s="17"/>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
     </row>
     <row r="99" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H99" s="17"/>
-      <c r="I99" s="17"/>
-      <c r="J99" s="17"/>
-      <c r="K99" s="17"/>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
     </row>
     <row r="100" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H100" s="17"/>
-      <c r="I100" s="17"/>
-      <c r="J100" s="17"/>
-      <c r="K100" s="17"/>
+      <c r="H100" s="15"/>
+      <c r="I100" s="15"/>
+      <c r="J100" s="15"/>
+      <c r="K100" s="15"/>
     </row>
     <row r="101" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H101" s="17"/>
-      <c r="I101" s="17"/>
-      <c r="J101" s="17"/>
-      <c r="K101" s="17"/>
+      <c r="H101" s="15"/>
+      <c r="I101" s="15"/>
+      <c r="J101" s="15"/>
+      <c r="K101" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1484,18 +1460,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:F5"/>
+  <dimension ref="A2:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1509,7 +1483,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1521,12 +1495,10 @@
       </c>
       <c r="D3" s="5">
         <f>C3/'Material streams'!$D$10</f>
-        <v>3.6440009345636501E-2</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.644000933957018E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -1538,12 +1510,10 @@
       </c>
       <c r="D4" s="5">
         <f>C4/'Material streams'!$D$10</f>
-        <v>1.3834859735727234E-2</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-    </row>
-    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.3834859733424085E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="12" t="s">
         <v>9</v>
@@ -1552,12 +1522,10 @@
         <f>SUM(C3:C4)</f>
         <v>1885.3113149999999</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <f>SUM(D3:D4)</f>
-        <v>5.0274869081363735E-2</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+        <v>5.0274869072994263E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1607,7 +1575,7 @@
       </c>
       <c r="D2" s="4">
         <f>C2/'Material streams'!$D$10</f>
-        <v>7.098805018668882</v>
+        <v>7.0988050174871136</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -1616,19 +1584,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="4">
-        <v>169540876.71041501</v>
+        <v>169540876.71570799</v>
       </c>
       <c r="C3" s="4">
         <f>B3/B9/E9</f>
-        <v>8106185.8336320836</v>
+        <v>8106185.8338851538</v>
       </c>
       <c r="D3" s="4">
         <f>C3/'Material streams'!$D$10</f>
-        <v>216.16452852777707</v>
-      </c>
-      <c r="E3" s="19">
+        <v>216.16452849853974</v>
+      </c>
+      <c r="E3" s="17">
         <f>B3/1000/'Material streams'!D10</f>
-        <v>4.5210811141584566</v>
+        <v>4.5210811135469591</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
